--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -815,7 +815,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn các rule dùng outcome nhưng không mở rộng data risk.</t>
+          <t>Chính sách tail-sampling hiệu quả khi lưu lượng lớn và buffer hữu hạn: (a) Giữ lại 100% các vết có lỗi, độ trễ cao hoặc chi phí bất thường, (b) lấy mẫu lưu lượng bình thường theo ngân sách cố định, (c) đặt giới hạn buffer để chống tràn bộ nhớ và ghi nhận rõ tỷ lệ lấy mẫu.</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Sequential dependency, External waiting.</t>
+          <t>Biểu đồ waterfall cho thấy tool A và tool B chạy tuần tự mất 2s + 2s dù hoàn toàn độc lập; mẫu hình tắc nghẽn là thực thi nối tiếp (serial execution) và giải pháp tối ưu là chạy song song hai công cụ.</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Prompt name/label/version, Resolved source.</t>
+          <t>Nhãn 'production' là tham chiếu động; để bảo đảm khả năng kiểm toán và phục hồi chính xác, hệ thống telemetry bắt buộc phải ghi lại mã băm (hash) hoặc số phiên bản cụ thể của prompt đã được phân giải.</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Collector, Metric route.</t>
+          <t>Để loại bỏ tình trạng duplicate dữ liệu trace khi gửi trực tiếp và qua collector, kiến trúc chuẩn là định tuyến toàn bộ telemetry qua một OpenTelemetry Collector duy nhất và cấu hình fan-out rõ ràng tại đó.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Request counter, Latency observation.</t>
+          <t>Ghi nhận chỉ số đo lường chính xác: Tăng bộ đếm request ngay khi tiếp nhận (ingress), đo thời gian xử lý trong khối `finally`, và chỉ gắn nhãn thành công/thất bại tại sự kiện kết thúc cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>50000000000000</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
@@ -1377,7 +1381,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nhân số giá trị độc lập của từng label.</t>
+          <t>Upper bound số time series: Tích số các giá trị cardinality của từng metric label = 1.000.000 (user_id) * 10.000.000 (request_id) * 5 (model) = 5 * 10^13 = 50.000.000.000.000 series.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -676,10 +676,30 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra SDK instrumentation, Collector boundary.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra SDK instrumentation, Collector boundary.</t>
+- 1.0đ: Đặc tả đầy đủ 5 thành phần kiến trúc: SDK chuẩn OTLP, Collector Receiver, Processor, Exporter, và Backend.
+- 1.0đ: Thiết kế khâu Processor thực hiện khử khuẩn PII tập trung trước khi phát tán dữ liệu ra bên ngoài.
+- 1.0đ: Cấu hình Exporter hỗ trợ fan-out đa đích độc lập cho metrics, logs và traces.
+- 1.0đ: Trình bày quy trình di chuyển (migration behavior) chứng minh 0% thay đổi code và không downtime.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Kiến trúc OpenTelemetry Trung lập với Nhà cung cấp (Vendor-neutral Architecture):
+- **App / SDK Layer**: Ứng dụng tích hợp OpenTelemetry SDK chuẩn mã nguồn mở (OTel Python/Go/Java SDK), sử dụng giao thức chuẩn OTLP (OpenTelemetry Protocol qua gRPC/HTTP). Không import bất kỳ vendor SDK chuyên biệt nào (như Datadog SDK, New Relic SDK).
+- **Collector Layer (OTel Collector Deployment)**:
+  + **Receiver**: Tiếp nhận OTLP metrics, logs, traces trên cổng 4317/4318.
+  + **Processor (Bắt buộc)**:
+    * `memory_limiter`: Ngăn chặn tràn RAM collector khi traffic cao.
+    * `redaction processor` / `transform processor`: Khử khuẩn PII tập trung (mask email, phone, token) trước khi dữ liệu rời khỏi hạ tầng nội bộ.
+    * `batch processor`: Gom cụm dữ liệu để tối ưu hóa băng thông truyền tải.
+  + **Exporter**: Cấu hình các exporter song song để fan-out sang các hệ thống lưu trữ chuyên biệt (e.g., Prometheus/Loki/Tempo hoặc Cloud Vendor).
+  + **Backend**: Lưu trữ dữ liệu tại các kho tương ứng.
+2. Hành vi Chuyển đổi Nhà cung cấp (Migration Behavior - Zero Downtime &amp; Zero Code Change):
+- Khi cần chuyển từ Backend A sang Backend B (hoặc từ On-prem sang Cloud SaaS):
+  + **Code ứng dụng**: Giữ nguyên 100%, không cần sửa đổi dù chỉ 1 dòng code, không cần re-deploy ứng dụng.
+  + **Collector Configuration**: Chỉ cần cập nhật file YAML cấu hình của OTel Collector (thêm exporter B, chạy kép A và B trong giai đoạn song song, sau đó xóa exporter A).
+  + Đảm bảo chuyển đổi diễn ra mượt mà, không gián đoạn dịch vụ và tránh hoàn toàn nguy cơ bị khóa chặt nhà cung cấp (vendor lock-in).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sức mạnh cốt lõi của OpenTelemetry là sự trung lập về công nghệ (Vendor Neutrality). Bằng cách tách rời khâu sinh dữ liệu (Instrumented App) và khâu chuyển tiếp dữ liệu (Collector Processors &amp; Exporters), doanh nghiệp có toàn quyền kiểm soát dữ liệu của mình: khử khuẩn PII tập trung một nơi, điều phối dữ liệu đến nhiều đích khác nhau, và thay đổi nhà cung cấp backend chỉ bằng một thao tác sửa file cấu hình YAML mà không cần chạm vào mã nguồn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Collector Architecture &amp; Configuration (https://opentelemetry.io/docs/collector/architecture/) &amp; CNCF OpenTelemetry Project</t>
         </is>
       </c>
     </row>
@@ -758,10 +778,26 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Operation name, Provider/model.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Operation name, Provider/model.</t>
+- 1.0đ: Định nghĩa chuẩn xác các thuộc tính Model Identity theo OpenTelemetry semconv.
+- 1.0đ: Định nghĩa chuẩn xác các thuộc tính Token Usage và Finish Reason theo chuẩn quốc tế.
+- 1.0đ: Thiết kế cơ chế Opt-in bảo vệ nội dung (mặc định tắt content capture, chỉ bật khi có cấu hình an toàn).
+- 1.0đ: Xây dựng quy trình kiểm tra hợp chuẩn (Validation Pipeline) phát hiện vi phạm quy ước ngữ nghĩa.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hợp đồng Ngữ nghĩa Trace GenAI (GenAI Trace Semantic Contract) có Phiên bản và Kiểm định:
+1. **Bảng ánh xạ thuộc tính chuẩn (OpenTelemetry GenAI Semantic Attributes v1.28+)**:
+- **Model Identity**: `gen_ai.system = 'openai'`, `gen_ai.request.model = 'gpt-4o'`, `gen_ai.response.model = 'gpt-4o-2024-08-06'`, `gen_ai.request.temperature = 0.2`.
+- **Token Usage**: `gen_ai.usage.input_tokens = 450`, `gen_ai.usage.output_tokens = 120`, `gen_ai.usage.total_tokens = 570`.
+- **Finish Reason**: `gen_ai.response.finish_reasons = ['tool_calls']` (hoặc `['stop']`, `['length']`, `['content_filter']`).
+- **Tool Relation**: `gen_ai.tool.name = 'order_lookup'`, `gen_ai.tool.call_id = 'call_abc123'`.
+2. **Chính sách Opt-in Bắt buộc cho Nội dung (Content Capture Policy)**:
+- Mặc định: `capture_message_content = false`. Không lưu nội dung chuỗi của prompt và completion.
+- Chỉ khi cấu hình biến môi trường `OTEL_GENAI_CAPTURE_MESSAGE_CONTENT=true` (trong môi trường staging có kiểm soát hoặc opt-in rõ ràng từ khách hàng), span mới được phép ghi `gen_ai.prompt` và `gen_ai.completion`.
+3. **Kiểm tra Xác thực Hợp đồng (Validation Pipeline)**:
+- Tại Collector, tích hợp bộ kiểm tra `schema_validator`: kiểm tra xem các span có tên bắt đầu bằng `gen_ai.` có bắt buộc chứa đủ 4 trường cốt lõi (`gen_ai.system`, `gen_ai.request.model`, `gen_ai.usage.total_tokens`, `finish_reasons`) hay không. Nếu thiếu, tăng metric `otel_semconv_validation_failures_total` để nhắc nhở team phát triển.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+OpenTelemetry đã ban hành quy chuẩn ngữ nghĩa chính thức dành riêng cho GenAI (Semantic Conventions for Generative AI Operations). Việc tuân thủ các quy ước chuẩn này giúp các công cụ trực quan hóa (như Jaeger, Datadog, Honeycomb, Langfuse) có thể tự động hiểu và vẽ nên biểu đồ chi phí token, thời gian phản hồi của model, và lý do ngắt câu mà không cần viết custom parser. Chính sách opt-in nội dung bảo đảm tuân thủ quy chuẩn quyền riêng tư toàn cầu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Semantic Conventions for Generative AI Operations (https://opentelemetry.io/docs/specs/semconv/gen-ai/) &amp; CNCF Standards</t>
         </is>
       </c>
     </row>
@@ -846,10 +882,29 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Head decision timing, Tail decision timing.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Head decision timing, Tail decision timing.</t>
+- 1.0đ: Thiết kế kiến trúc lấy mẫu hai tầng (Head Sampling giảm tải tại SDK + Tail Sampling chọn lọc tại Collector).
+- 1.0đ: Đặc tả chính sách giữ lại 100% ca lỗi kỹ thuật (ERROR, 5xx) và ca trễ đuôi (P95 latency).
+- 1.0đ: Bảo vệ bộ đệm Collector chống tràn RAM (memory limiter, adaptive sampling window).
+- 1.0đ: Thực thi nghiêm ngặt chính sách quyền riêng tư (loại bỏ raw content trước khi ghi đĩa).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Chính sách Lấy mẫu Trace Định hướng Kết quả (Outcome-aware Trace Sampling Policy) cho Lưu lượng Cao và Bộ đệm Hữu hạn:
+1. **Chiến lược Hai tầng (Head + Tail Sampling Architecture)**:
+- **Tầng 1: Head Sampling tại SDK (Giảm tải cho Collector Buffer)**:
+  + Với traffic khổng lồ, nếu đẩy 100% trace vào collector để chờ phân tích, bộ đệm (in-memory buffer) của collector sẽ bị tràn (OOM drop).
+  + Áp dụng Head Sampling xác suất 10% ngay tại client SDK đối với các request thông thường, chỉ cho phép 10% lưu lượng đi vào collector.
+  + **Ngoại lệ ưu tiên (Bypass rule)**: Bất kỳ request nào có header đánh dấu `priority=high` hoặc tenant quan trọng sẽ được bypass head-sampling để đi thẳng vào collector.
+- **Tầng 2: Tail Sampling tại Collector (Giữ lại 100% Ca Sự cố &amp; Bất thường)**:
+  + Bộ đệm collector gom các spans trong cửa sổ 15 giây.
+  + Giữ lại **100% trace có lỗi** (`status_code &gt;= 500` hoặc span `status == ERROR`).
+  + Giữ lại **100% trace có độ trễ đuôi** (`latency &gt; P95`).
+  + Giữ lại **100% trace có số lần retry công cụ cao** (`tool_retry_count &gt;= 2`).
+  + Với các trace thành công bình thường còn lại trong bộ đệm: chỉ lấy mẫu 1% để làm baseline so sánh.
+2. **Tuân thủ Chính sách Quyền riêng tư (Privacy Enforcement)**:
+- Trước khi trace được lưu vào kho lưu trữ (Tempo/S3), bộ lọc `transform processor` thực thi kiểm tra cuối cùng: loại bỏ vĩnh viễn mọi trường `raw_prompt`, `raw_completion`, và `user_credentials`, bảo đảm 100% trace được lưu không chứa nội dung thô.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống lưu lượng lớn, nếu chỉ dùng Tail Sampling, lượng trace đổ về sẽ đè bẹp bộ nhớ đệm của Collector; ngược lại nếu chỉ dùng Head Sampling ngẫu nhiên, các ca lỗi hiếm gặp (0.1% lỗi) sẽ bị bỏ sót gần hết. Sự kết hợp giữa Head Sampling giảm tải bước đầu và Tail Sampling thông minh theo kết quả (lỗi, chậm, retry) vừa bảo vệ an toàn cho hạ tầng Collector vừa bảo đảm 100% các sự cố nghiêm trọng đều được lưu vết đầy đủ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Collector Tail Sampling Configuration &amp; Datadog Trace Ingestion Control</t>
         </is>
       </c>
     </row>
@@ -928,10 +983,22 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Sequential dependency, External waiting.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Sequential dependency, External waiting.</t>
+- 1.0đ: Phân loại chính xác mô hình bottleneck là Schema Validation Failure Retry Loop (lặp do lỗi schema).
+- 1.0đ: Phân tích lập luận thuyết phục dựa trên đặc điểm span ngắn và số lần lặp lại (5 lần).
+- 1.0đ: Thiết kế bước kiểm chứng đối soát payload thực tế với schema kỳ vọng.
+- 1.0đ: Xây dựng kế hoạch unit test giả lập để tái hiện và khắc phục dứt điểm nguyên nhân gốc.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Mô hình Bottleneck trong Trace:
+- Đây là mô hình **Repeated-Call do Lỗi Schema / Chết vòng lặp sửa sai (Schema Validation Failure Retry Loop)**.
+- Đặc điểm nhận diện trên trace waterfall: Tool được gọi liên tiếp 5 lần với thời gian thực thi của mỗi lần gọi rất ngắn (short duration, vài chục ms). Nguyên nhân không phải do mạng chậm hay database nặng (nếu mạng/db chậm thì duration của tool phải dài), mà do kết quả trả về từ tool không khớp với JSON schema mà Agent mong đợi (ví dụ: thiếu required field hoặc sai kiểu dữ liệu), khiến Agent lập tức thử lại (re-invocation) với hy vọng sửa sai, dẫn đến 5 lời gọi ngắn ngủi liên tục trước khi cạn số lần retry.
+2. Kế hoạch Kiểm chứng Xác minh (Verification Plan):
+- **Bước 1 - Kiểm tra Payload và Schema Log**: Trích xuất log chi tiết của 5 lần gọi tool trong trace: đối chiếu `tool_response_payload` với `expected_tool_schema`. Xác định chính xác trường dữ liệu nào bị thiếu hoặc sai định dạng (ví dụ: trường `date` trả về chuỗi ISO thay vì timestamp số nguyên).
+- **Bước 2 - Kiểm tra Lời nhắc Tự sửa của Agent (Re-prompt Inspection)**: Kiểm tra input prompt của các lần gọi thứ 2, 3, 4, 5 xem Agent có nhận thức được lỗi schema không hay chỉ mù quáng gửi lại cùng một câu lệnh.
+- **Bước 3 - Unit Test Tái lập (Regression Reproduce)**: Viết unit test giả lập đúng mock response bị sai schema từ tool và chạy Agent để xác nhận hành vi lặp 5 lần được tái hiện 100%.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi chẩn đoán nút thắt cổ chai trong Trace của AI Agent, thời gian chạy của span mang tính quyết định: Một span dài bất thường chỉ ra vấn đề về mạng hoặc hiệu năng tính toán (performance bottleneck). Ngược lại, nhiều span liên tiếp cực ngắn chỉ ra lỗi logic ở khâu xác thực dữ liệu (contract validation failure) - hệ thống vừa nhận dữ liệu xong thì parser văng exception, buộc vòng lặp phải quay lại ngay lập tức. Xác định đúng mô hình giúp tiết kiệm hàng giờ tối ưu mạng vô ích.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Brendan Gregg: Systems Performance: Enterprise and the Cloud &amp; LangChain Debugging Documentation</t>
         </is>
       </c>
     </row>
@@ -1010,10 +1077,29 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Prompt name/label/version, Resolved source.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Prompt name/label/version, Resolved source.</t>
+- 1.0đ: Thiết lập bằng chứng so sánh trực tiếp v6 vs v7 (gắn thẻ version trên trace, đo delta chất lượng và phản hồi).
+- 1.0đ: Xây dựng quy trình triển khai Canary phân tầng với soak time và automated health gates.
+- 1.0đ: Xác định tiêu chí kích hoạt rollback tự động rõ ràng dựa trên số liệu chất lượng.
+- 1.0đ: Thiết kế cơ chế rollback tức thì bằng feature flag/config động không cần redeploy mã nguồn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Bằng chứng So sánh, Triển khai Canary và Hoàn nguyên (Compare, Rollout, Rollback Evidence):
+1. **Bằng chứng So sánh Đối đầu (Direct Comparison Evidence)**:
+- Gắn thẻ phiên bản bắt buộc trên mọi trace: `prompt_version = 'v6'` (baseline) và `prompt_version = 'v7'` (canary).
+- Lấy mẫu các cặp request có cùng input hoặc chạy song song (shadow/canary 10% traffic):
+  + Đo lường delta chất lượng: `groundedness_score_v7 - groundedness_score_v6 = -0.15` (sụt giảm 15%).
+  + Đo lường tỷ lệ người dùng phàn nàn: `negative_feedback_rate_v7 = 8.5%` so với `v6 = 1.2%`.
+  + Thu thập 20 trace mẫu đối chứng cụ thể chỉ ra vị trí v7 bịa đặt thông tin trong khi v6 trả lời chính xác.
+2. **Quy trình Triển khai Canary có Kiểm soát (Controlled Canary Rollout)**:
+- Phân bổ traffic theo tỷ lệ: 5% -&gt; 10% -&gt; 25% -&gt; 50% -&gt; 100% kèm thời gian ngâm (soak time) tối thiểu 2 giờ tại mỗi nấc.
+- Đặt Automated Health Gates tại mỗi bước: nếu các chỉ số chất lượng ngữ nghĩa hoặc lỗi nghiệp vụ vượt ngưỡng, quá trình tăng traffic bị đóng băng ngay lập tức.
+3. **Bằng chứng &amp; Cơ chế Hoàn nguyên Tức thì (Instant Rollback Execution)**:
+- **Tiêu chí Rollback khẩn cấp**: Kích hoạt khi `canary_negative_feedback_rate &gt; 3%` hoặc `faithfulness_score &lt; 0.85` trong cửa sổ 15 phút.
+- **Cơ chế thực thi**: Rollback bằng cờ cấu hình động (Feature Flag / Dynamic Config) chuyển 100% traffic về `prompt_version = 'v6'` trong vòng dưới 30 giây mà không cần redeploy code container.
+- **Bằng chứng sau hoàn nguyên**: Dashboard ghi nhận tỷ lệ lỗi và phàn nàn lập tức hạ nhiệt về mức baseline ban đầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khác với phần mềm truyền thống nơi việc thay đổi code được quản lý chặt chẽ qua Git commit, trong ứng dụng GenAI, prompt chính là logic nghiệp vụ cốt lõi. Một sự thay đổi prompt từ v6 sang v7 có thể gây thảm họa suy giảm chất lượng âm thầm. Do đó, hệ thống giám sát phải hỗ trợ khả năng truy vết phiên bản prompt (Prompt Version Traceability) trên từng trace, triển khai theo cơ chế Canary phân tầng và có công tắc hoàn nguyên tức thời bằng feature flag.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Canarying Releases &amp; Arize AI: Prompt Versioning and Evaluation</t>
         </is>
       </c>
     </row>
@@ -1092,10 +1178,24 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Signal coverage, Existing stack/team skill.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Signal coverage, Existing stack/team skill.</t>
+- 1.0đ: Xây dựng ma trận so sánh đầy đủ các tiêu chí cốt lõi (air-gapped compliance, SRE fit, LLM eval features).
+- 1.0đ: Phân tích và loại trừ dứt khoát giải pháp Cloud SaaS do vi phạm ràng buộc air-gapped.
+- 1.0đ: Đánh giá đúng điểm mạnh/yếu của ngăn xếp Prometheus/Grafana truyền thống đối với ứng dụng AI.
+- 1.0đ: Đưa ra đề xuất lựa chọn khả thi, thuyết phục (kết hợp công cụ self-hosted chuyên dụng với hạ tầng SRE có sẵn).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Lập Ma trận Quyết định Lựa chọn Stack Giám sát (Observability Stack Decision Matrix) cho Đội ngũ SRE mạnh và Môi trường Cách ly (Air-gapped Workload):
+| Tiêu chí Đánh giá | Phương án A: Cloud SaaS (Datadog / LangSmith Cloud) | Phương án B: Self-hosted LLM Platform (Langfuse / Arize Phoenix Self-hosted) | Phương án C: Standard Cloud-Native SRE Stack (Prometheus + Loki + Tempo) |
+| :--- | :--- | :--- | :--- |
+| **Tuân thủ Air-gapped (Bắt buộc)** | **LOẠI BỎ (FAIL)**: Đòi hỏi đẩy dữ liệu ra Internet công cộng, vi phạm 100% quy chuẩn cách ly | **ĐẠT (PASS)**: Hỗ trợ triển khai hoàn toàn on-premise qua Docker/Kubernetes, không cần kết nối mạng ngoài | **ĐẠT (PASS)**: Triển khai 100% nội bộ, hoàn toàn tương thích môi trường air-gapped |
+| **Tận dụng Năng lực SRE hiện có** | Thấp: Đội SRE phải học nền tảng SaaS mới | Vừa: Cần vận hành thêm container và Postgres của Langfuse | **RẤT CAO**: Đội ngũ SRE đã thành thạo PromQL, LogQL, Grafana, alerts |
+| **Tính năng Đánh giá LLM / Tracing chuyên sâu** | Rất cao nhưng không khả dụng | **RẤT CAO**: Có sẵn UI chấm điểm eval, playground, prompt tracking, token cost analytics | Trung bình: Cần tự thiết kế dashboard Grafana và tự viết pipeline eval |
+**Khuyến nghị Lựa chọn Kết hợp Tối ưu (Hybrid Best-Fit Recommendation)**:
+- **Kiến trúc đề xuất**: Kết hợp **Phương án B (Langfuse Self-hosted)** cho tầng AI Application/Eval Traces VÀ **Phương án C (Prometheus/Grafana)** cho tầng Hạ tầng/Hệ thống SRE.
+- **Lập luận bảo vệ**: Langfuse self-hosted đáp ứng trọn vẹn yêu cầu bảo mật air-gapped và cung cấp sẵn giao diện đánh giá LLM chuyên sâu; trong khi đó Prometheus/Grafana sẵn có của đội SRE sẽ tiếp nhận các metrics hạ tầng và quản lý cảnh báo tập trung.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi lựa chọn công nghệ giám sát, các ràng buộc kỹ thuật cứng (Hard Constraints) như môi trường cách ly (Air-gapped) có quyền phủ quyết tuyệt đối các giải pháp Cloud SaaS. Đồng thời, tận dụng tối đa thế mạnh sẵn có của đội ngũ (SRE capabilities) kết hợp với công cụ mã nguồn mở chuyên dụng cho LLM có thể tự lưu trữ (self-hosted) là chiến lược tối ưu nhất để vừa bảo đảm an toàn dữ liệu vừa có đầy đủ tính năng phân tích AI chuyên sâu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Langfuse Open Source Self-Hosting Documentation (https://langfuse.com/docs/deployment/self-host) &amp; CNCF Air-gapped Best Practices</t>
         </is>
       </c>
     </row>
@@ -1174,10 +1274,28 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Collector, Metric route.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Collector, Metric route.</t>
+- 1.0đ: Thiết kế kiến trúc fan-out tại Collector với các pipeline độc lập cho Prometheus, Loki và Tempo.
+- 1.0đ: Thống nhất ngữ nghĩa correlation (giữ nguyên service.name, trace_id, environment xuyên suốt 3 tín hiệu).
+- 1.0đ: Xây dựng cơ chế phát hiện đường truyền bị thất thoát tín hiệu (signal drop detection qua cross-validation).
+- 1.0đ: Xây dựng cơ chế ngăn ngừa và phát hiện gửi trùng lặp dữ liệu (duplicate prevention).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Định tuyến Tín hiệu (Collector Signal Fanout) và Cơ chế Phát hiện Đường truyền Thiếu/Trùng lặp:
+1. **Thiết kế Định tuyến tại OpenTelemetry Collector (Fanout Pipelines)**:
+- **Tiếp nhận chung (Single Ingestion)**: Cấu hình `otlp` receiver tiếp nhận toàn bộ dữ liệu trên port 4317/4318 mang chung W3C context (`trace_id`, `span_id`).
+- **Bộ xử lý chung (Shared Processors)**: Định tuyến qua `memory_limiter`, `redaction` (khử PII), và `batch` processor để đảm bảo tính nhất quán.
+- **Định tuyến chuyên biệt (Dedicated Exporters)**:
+  + Pipeline Metrics: OTLP Receiver -&gt; Processors -&gt; `prometheus` exporter (chuyển đổi OTLP metrics thành Prometheus format với labels chuẩn).
+  + Pipeline Logs: OTLP Receiver -&gt; Processors -&gt; `loki` exporter (chuyển đổi OTLP logs thành Loki streams, trích xuất `trace_id` thành structured metadata).
+  + Pipeline Traces: OTLP Receiver -&gt; Processors -&gt; `otlp/tempo` exporter (gửi OTLP traces tới Grafana Tempo).
+2. **Thống nhất Ngữ nghĩa Liên kết (Correlation Semantics)**:
+- Tất cả 3 pipeline bắt buộc phải giữ nguyên các trường định danh cốt lõi: `service.name`, `deployment.environment`, và đặc biệt là `trace_id` trong log và span.
+3. **Phát hiện Đường truyền Thiếu hoặc Trùng lặp (Missing/Duplicate Detection)**:
+- **Phát hiện Thiếu (Missing Signal Path)**: Thiết lập kiểm tra đối soát (cross-validation alert): nếu metric `http_requests_total` ghi nhận 1.000 requests nhưng Loki chỉ ghi nhận 500 logs hoặc Tempo chỉ có 800 spans, kích hoạt alert `TELEMETRY_PIPELINE_DROP` để kiểm tra exporter bị nghẽn.
+- **Phát hiện Trùng lặp (Duplicate Detection)**: Giám sát chỉ số nội tại của Collector `otelcol_processor_batch_send_failures` và sử dụng deduplication filter (dựa trên `trace_id` + `timestamp`) để ngăn chặn việc collector retry làm gửi trùng span sang Tempo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Fanout Signals trong OpenTelemetry: OpenTelemetry Collector đóng vai trò là tổng đài điều phối (traffic controller). Một request đi vào sẽ sinh ra đồng thời metrics, logs và traces. Nếu định tuyến không chuẩn, ngữ nghĩa liên kết (correlation) sẽ bị gãy vụn: vào Grafana xem trace không nhảy sang được log tương ứng trong Loki, hoặc từ metric lỗi không bấm vào xem trace được trong Tempo. Hệ thống giám sát phải bảo đảm sự đồng bộ tuyệt đối về labels và trường correlation xuyên suốt các nhánh exporter.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Grafana Observability Stack Integration Guide (Prometheus, Loki, Tempo) &amp; OpenTelemetry Collector Pipelines</t>
         </is>
       </c>
     </row>
@@ -1260,10 +1378,29 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Counter, Gauge.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Counter, Gauge.</t>
+- 1.0đ: Chọn chính xác Metric Type cho cả 3 đại lượng: Counter cho Cache Hit, Gauge cho Queue Depth, Histogram cho TTFT.
+- 1.0đ: Mô tả chuẩn xác cơ chế cập nhật kỹ thuật tương ứng (.inc(), .set(), .observe()).
+- 1.0đ: Viết đúng cú pháp 3 câu truy vấn PromQL phục vụ rate, current, và P95 histogram quantile.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Loại Metric Prometheus (Prometheus Metric Types Selection):
+- **Cache Hit Total**: Chọn **Counter** (`cache_hits_total`).
+  + Bản chất: Đây là giá trị chỉ tăng tích lũy theo thời gian (hoặc reset về 0 khi restart service). Không bao giờ giảm.
+- **Queue Depth**: Chọn **Gauge** (`inference_queue_depth`).
+  + Bản chất: Đây là giá trị tức thời có thể biến động tăng hoặc giảm bất kỳ lúc nào tùy thuộc vào tải của hàng đợi.
+- **TTFT (Time to First Token)**: Chọn **Histogram** (`llm_time_to_first_token_seconds_bucket`).
+  + Bản chất: Thời gian đáp ứng là biến liên tục có phân phối không đều; cần phân chia thành các khoảng (buckets) để tính toán chính xác các phân vị P50, P90, P95.
+2. Cơ chế Cập nhật (Instrument Update Mechanism):
+- `cache_hits_total.inc()`: Gọi hàm tăng 1 đơn vị mỗi khi có request đọc trúng cache.
+- `inference_queue_depth.set(current_depth)`: Cập nhật giá trị số lượng request đang chờ trong queue định kỳ hoặc mỗi khi có enqueue/dequeue.
+- `llm_time_to_first_token_seconds.observe(duration_seconds)`: Ghi nhận thời gian đo được cho token đầu tiên vào histogram.
+3. Câu lệnh Truy vấn PromQL (PromQL Queries cho Dashboard):
+- Tần suất đọc trúng cache (Rate): `rate(cache_hits_total[5m])` (số hit/giây trong 5 phút gần nhất).
+- Độ sâu hàng đợi hiện tại (Current): `inference_queue_depth` (hoặc `avg_over_time(inference_queue_depth[1m])`).
+- Phân vị P95 của TTFT (P95 Quantile): `histogram_quantile(0.95, sum(rate(llm_time_to_first_token_seconds_bucket[5m])) by (le))`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chọn sai loại metric trong Prometheus là lỗi kỹ thuật rất phổ biến. Nếu chọn sai Gauge cho Cache Hit, hàm `rate()` sẽ cho kết quả sai lệch khi có restart. Nếu không dùng Histogram cho TTFT mà dùng Gauge lưu giá trị trung bình, hệ thống sẽ hoàn toàn mất khả năng quan sát độ trễ đuôi (tail latency) qua hàm `histogram_quantile`. Tuân thủ đúng chuẩn Counter-Gauge-Histogram bảo đảm PromQL vận hành chính xác và cung cấp dữ liệu tin cậy cho bảng điều khiển.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Prometheus Documentation: Metric Types (https://prometheus.io/docs/concepts/metric_types/) &amp; PromQL Basics</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1479,31 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Request counter, Latency observation.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Request counter, Latency observation.</t>
+- 1.0đ: Thiết lập instrumentation cho cấp độ Request tổng thể (status, total duration).
+- 1.0đ: Thiết lập instrumentation cho từng Attempt đơn lẻ (ghi nhận 2 lần lỗi và 1 lần thành công với attempt_index).
+- 1.0đ: Thu thập đầy đủ token consumption của toàn bộ các lần thử, không bỏ sót token của các lần retry thất bại.
+- 1.0đ: Phân lập chỉ số tài nguyên lãng phí (wasted tokens / retry overhead) phục vụ tối ưu hóa chi phí.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Điểm Thu thập Metric (Instrumentation Points) cho Request có 2 Model Retries và Cuối cùng Thành công:
+1. **Cấp độ Toàn thể Yêu cầu (Request-level Instrumentation)**:
+- `agent_requests_total{status='success'}`: Tăng 1 đơn vị tại thời điểm kết thúc toàn bộ luồng xử lý.
+- `agent_request_duration_seconds.observe(total_elapsed)`: Đo tổng thời gian từ khi nhận request đến khi trả lời người dùng (bao gồm thời gian của cả 3 lần gọi model).
+2. **Cấp độ Lần thử Mô hình (Attempt-level Instrumentation)**:
+- `model_call_attempts_total{attempt_index='1', status='error', error_type='timeout'}`: Tăng 1 tại lần thử đầu tiên bị lỗi.
+- `model_call_attempts_total{attempt_index='2', status='error', error_type='rate_limit'}`: Tăng 1 tại lần thử thứ hai bị lỗi.
+- `model_call_attempts_total{attempt_index='3', status='success', error_type='none'}`: Tăng 1 tại lần thử thứ ba thành công.
+- `model_attempt_duration_seconds.observe(elapsed)`: Ghi nhận thời gian thực thi riêng biệt của từng attempt đơn lẻ.
+3. **Cấp độ Token và Chi phí (Token Consumption Instrumentation)**:
+- Không chỉ ghi nhận token của lần thử thành công! Bắt buộc phải cộng dồn và phát thải token của **TẤT CẢ CÁC LẦN THỬ**:
+  + `llm_tokens_consumed_total{type='prompt', attempt='1'}` += tokens_attempt_1.
+  + `llm_tokens_consumed_total{type='prompt', attempt='2'}` += tokens_attempt_2.
+  + `llm_tokens_consumed_total{type='prompt', attempt='3'}` += tokens_attempt_3.
+  + `llm_tokens_consumed_total{type='completion', attempt='3'}` += tokens_attempt_3.
+  + `agent_request_wasted_tokens_total`: Tăng bằng tổng token của attempt 1 và attempt 2 để đo lường lượng tài nguyên bị lãng phí do lỗi tạm thời.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống Agentic AI, việc chỉ instrument kết quả cuối cùng là một thiếu sót nghiêm trọng. Một request thành công sau 2 lần retry có thể đã ngầm tiêu tốn gấp 3 lần chi phí token và làm tăng độ trễ lên gấp 3 lần mà dashboard tổng quát không phát hiện ra. Bằng cách đặt instrumentation points ở cả tầng Request (tổng thể) và tầng Attempt (từng nỗ lực), kỹ sư có thể nhìn thấy rõ tỷ lệ hao tổn tài nguyên (wasted tokens) và hiệu quả của chính sách retry.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Metrics Data Model &amp; Google SRE Workbook: Non-Abstract Large System Design</t>
         </is>
       </c>
     </row>
@@ -1412,10 +1570,26 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Tổ hợp Cartesian của label, Bounded label.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Tổ hợp Cartesian của label, Bounded label.</t>
+- 1.0đ: Phân tích đúng nguyên nhân bùng nổ cardinality do đưa request_id vào metric labels.
+- 1.0đ: Thiết kế hợp đồng Metric chỉ giữ các nhãn low-cardinality (tenant, feature, model).
+- 1.0đ: Định tuyến high-cardinality details (request_id, payloads) sang Structured Logs/Traces chuyên dụng.
+- 1.0đ: Thiết lập quy trình truy vấn chéo (cross-system drilldown qua Data Links/Exemplars) từ metric sang trace cụ thể.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa đổi Hợp đồng Label/Event để Kiểm soát Cardinality (Metric vs Log Separation):
+- **Nguyên nhân cốt lõi**: Việc đưa các giá trị định danh duy nhất (như `request_id`, `session_id`, `user_id`, `prompt_hash`) vào Prometheus Metric Labels gây ra hiện tượng **Bùng nổ Cardinality (Cardinality Explosion)**, làm sập bộ nhớ TSDB (Prometheus/Thanos).
+- **Hợp đồng Metric Chuẩn hóa (Low-Cardinality Dimensions)**:
+  Chỉ giữ lại các nhãn có tập giá trị hữu hạn, có thể đếm được:
+  `agent_cost_usd_total{tenant_id='tenant_A', feature='medical_summary', model='gpt-4o'}`.
+  (Tuyệt đối cấm gán `request_id` vào metric label).
+- **Hợp đồng Event / Trace Chuẩn hóa (High-Cardinality Store)**:
+  Các thông tin chi tiết của từng request cụ thể (`request_id`, `duration_ms`, `input_token`, `error_stack`) được phát thải vào **Structured Logs / Distributed Traces** (Loki, Elasticsearch, Tempo, ClickHouse) - những hệ thống được thiết kế chuyên biệt để đánh index dữ liệu cardinality vô tận.
+2. Xác minh Truy vấn Chéo (Cross-system Query Verification Workflow):
+- **Bước 1**: Trên Dashboard Grafana, sử dụng PromQL để phát hiện bất thường tổng quan: `sum(rate(agent_cost_usd_total[5m])) by (tenant_id, feature)` -&gt; Phát hiện tenant A có cost tăng vọt ở feature medical_summary.
+- **Bước 2**: Sử dụng Data Links trong Grafana để truyền các biến ngữ cảnh (`tenant_id`, `feature`, time range) sang truy vấn Loki/Tempo: `LogQL: {app='agent'} |= "tenant_A" |= "medical_summary"` để lấy chính xác danh sách các `request_id` cụ thể phục vụ debug.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy tắc vàng trong SRE: Metrics dùng để phát hiện xu hướng (Aggregations over bounded dimensions), còn Logs và Traces dùng để phân tích chi tiết (High-cardinality debugging). Cố tình đưa `request_id` vào Prometheus labels sẽ tạo ra hàng triệu time-series rác, làm tê liệt hệ thống giám sát. Giải pháp chuẩn mực là giữ metrics tinh gọn và sử dụng Data Links / Exemplars để bắc cầu sang logs/traces khi cần đào sâu vào từng request.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Prometheus Best Practices: Labels (https://prometheus.io/docs/practices/naming/#labels) &amp; Grafana Exemplars Documentation</t>
         </is>
       </c>
     </row>
